--- a/Stats Sheet/Round Gaps/Consumption.xlsx
+++ b/Stats Sheet/Round Gaps/Consumption.xlsx
@@ -88,6 +88,9 @@
     <x:t>24</x:t>
   </x:si>
   <x:si>
+    <x:t>25</x:t>
+  </x:si>
+  <x:si>
     <x:t>_ChrisMS</x:t>
   </x:si>
   <x:si>
@@ -169,6 +172,9 @@
     <x:t>1161</x:t>
   </x:si>
   <x:si>
+    <x:t>283</x:t>
+  </x:si>
+  <x:si>
     <x:t>OddishThoughts</x:t>
   </x:si>
   <x:si>
@@ -328,6 +334,9 @@
     <x:t>248</x:t>
   </x:si>
   <x:si>
+    <x:t>91</x:t>
+  </x:si>
+  <x:si>
     <x:t>TastyBaconZ</x:t>
   </x:si>
   <x:si>
@@ -346,6 +355,9 @@
     <x:t>109</x:t>
   </x:si>
   <x:si>
+    <x:t>157</x:t>
+  </x:si>
+  <x:si>
     <x:t>BigJedo</x:t>
   </x:si>
   <x:si>
@@ -361,12 +373,18 @@
     <x:t>927</x:t>
   </x:si>
   <x:si>
+    <x:t>1247</x:t>
+  </x:si>
+  <x:si>
     <x:t>DatGuyAdam</x:t>
   </x:si>
   <x:si>
     <x:t>1252</x:t>
   </x:si>
   <x:si>
+    <x:t>572</x:t>
+  </x:si>
+  <x:si>
     <x:t>JamestheDouglas</x:t>
   </x:si>
   <x:si>
@@ -601,6 +619,9 @@
     <x:t>497</x:t>
   </x:si>
   <x:si>
+    <x:t>807</x:t>
+  </x:si>
+  <x:si>
     <x:t>TheSheepMasters</x:t>
   </x:si>
   <x:si>
@@ -658,6 +679,9 @@
     <x:t>cherryblawsom</x:t>
   </x:si>
   <x:si>
+    <x:t>241</x:t>
+  </x:si>
+  <x:si>
     <x:t>flintflint04</x:t>
   </x:si>
   <x:si>
@@ -698,6 +722,12 @@
   </x:si>
   <x:si>
     <x:t>Nuclearsugar</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BEANJEE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Br8dy_</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -1056,10 +1086,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:AB119"/>
+  <x:dimension ref="A1:AC121"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:28" s="1" customFormat="1">
+    <x:row r="1" spans="1:29" s="1" customFormat="1">
       <x:c r="E1" s="1">
         <x:v>43840</x:v>
       </x:c>
@@ -1132,8 +1162,11 @@
       <x:c r="AB1" s="1">
         <x:v>46092</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:28">
+      <x:c r="AC1" s="1">
+        <x:v>46124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:29">
       <x:c r="F2" s="0">
         <x:v>56</x:v>
       </x:c>
@@ -1203,8 +1236,11 @@
       <x:c r="AB2" s="0">
         <x:v>59</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3" spans="1:28">
+      <x:c r="AC2" s="0">
+        <x:v>32</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:29">
       <x:c r="E3" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -1277,13 +1313,16 @@
       <x:c r="AB3" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4" spans="1:28">
+      <x:c r="AC3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:29">
       <x:c r="A4" s="0">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
         <x:v>0</x:v>
@@ -1292,110 +1331,113 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J4" s="0" t="s">
-        <x:v>26</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="N4" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="AB4" s="0" t="s">
-        <x:v>28</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:28">
+        <x:v>29</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:29">
       <x:c r="A5" s="0">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D5" s="0">
-        <x:v>24</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA5" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB5" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC5" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:29">
       <x:c r="A6" s="0">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>30</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
         <x:v>0</x:v>
@@ -1404,53 +1446,56 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G6" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:29">
       <x:c r="A7" s="0">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>31</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D7" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N7" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="X7" s="0" t="s">
-        <x:v>33</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="Y7" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB7" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:28">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AC7" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:29">
       <x:c r="A8" s="0">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
         <x:v>0</x:v>
@@ -1459,86 +1504,89 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I8" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="K8" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="P8" s="0" t="s">
-        <x:v>38</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:28">
+        <x:v>39</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:29">
       <x:c r="A9" s="0">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>39</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D9" s="0">
-        <x:v>15</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G9" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L9" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="S9" s="0" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="T9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V9" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="W9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA9" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB9" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC9" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:29">
       <x:c r="A10" s="0">
         <x:v>7</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
         <x:v>0</x:v>
@@ -1547,86 +1595,89 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I10" s="0" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="J10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M10" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P10" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W10" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="X10" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:29">
       <x:c r="A11" s="0">
         <x:v>8</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D11" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G11" s="0" t="s">
-        <x:v>40</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L11" s="0" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="M11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P11" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X11" s="0" t="s">
-        <x:v>50</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:28">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="AC11" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:29">
       <x:c r="A12" s="0">
         <x:v>9</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
         <x:v>0</x:v>
@@ -1635,18 +1686,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:29">
       <x:c r="A13" s="0">
         <x:v>10</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
         <x:v>0</x:v>
@@ -1655,33 +1706,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K13" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="L13" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N13" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:28">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:29">
       <x:c r="A14" s="0">
         <x:v>11</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
         <x:v>0</x:v>
@@ -1690,65 +1741,68 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H14" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="K14" s="0" t="s">
-        <x:v>53</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:28">
+        <x:v>55</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:29">
       <x:c r="A15" s="0">
         <x:v>12</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D15" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I15" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K15" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="R15" s="0" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="X15" s="0" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Z15" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AB15" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:28">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AC15" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:29">
       <x:c r="A16" s="0">
         <x:v>13</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>62</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
         <x:v>0</x:v>
@@ -1757,71 +1811,74 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H16" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="S16" s="0" t="s">
-        <x:v>63</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="T16" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:29">
       <x:c r="A17" s="0">
         <x:v>14</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>64</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
       <x:c r="D17" s="0">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K17" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S17" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="X17" s="0" t="s">
-        <x:v>66</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="AA17" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AB17" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC17" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:29">
       <x:c r="A18" s="0">
         <x:v>15</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
         <x:v>0</x:v>
@@ -1830,36 +1887,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O18" s="0" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="R18" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="S18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T18" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X18" s="0" t="s">
-        <x:v>71</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:28">
+        <x:v>73</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:29">
       <x:c r="A19" s="0">
         <x:v>16</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>72</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
         <x:v>0</x:v>
@@ -1868,15 +1925,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:29">
       <x:c r="A20" s="0">
         <x:v>17</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>73</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
         <x:v>0</x:v>
@@ -1885,27 +1942,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O20" s="0" t="s">
-        <x:v>74</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="P20" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U20" s="0" t="s">
-        <x:v>75</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:28">
+        <x:v>77</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:29">
       <x:c r="A21" s="0">
         <x:v>18</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
         <x:v>0</x:v>
@@ -1914,66 +1971,66 @@
         <x:v>18</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q21" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="R21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T21" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V21" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="X21" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Y21" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:29">
       <x:c r="A22" s="0">
         <x:v>19</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>79</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
         <x:v>1</x:v>
@@ -1982,39 +2039,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M22" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB22" s="0" t="s">
-        <x:v>80</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:28">
+        <x:v>82</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:29">
       <x:c r="A23" s="0">
         <x:v>20</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
         <x:v>1</x:v>
@@ -2023,27 +2080,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H23" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J23" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="L23" s="0" t="s">
-        <x:v>41</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:28">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:29">
       <x:c r="A24" s="0">
         <x:v>21</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
         <x:v>1</x:v>
@@ -2052,36 +2109,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I24" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="N24" s="0" t="s">
-        <x:v>84</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="R24" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="S24" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V24" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="W24" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z24" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:28">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:29">
       <x:c r="A25" s="0">
         <x:v>22</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
         <x:v>1</x:v>
@@ -2090,18 +2147,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I25" s="0" t="s">
-        <x:v>36</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:28">
+        <x:v>37</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:29">
       <x:c r="A26" s="0">
         <x:v>23</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
         <x:v>1</x:v>
@@ -2110,30 +2167,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J26" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB26" s="0" t="s">
-        <x:v>90</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:28">
+        <x:v>92</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:29">
       <x:c r="A27" s="0">
         <x:v>24</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>91</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
         <x:v>1</x:v>
@@ -2142,24 +2199,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G27" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H27" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I27" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:29">
       <x:c r="A28" s="0">
         <x:v>25</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
         <x:v>1</x:v>
@@ -2168,21 +2225,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L28" s="0" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="Q28" s="0" t="s">
-        <x:v>94</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:28">
+        <x:v>96</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:29">
       <x:c r="A29" s="0">
         <x:v>26</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>95</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
         <x:v>1</x:v>
@@ -2191,48 +2248,48 @@
         <x:v>12</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S29" s="0" t="s">
-        <x:v>96</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="T29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W29" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="X29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y29" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z29" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:29">
       <x:c r="A30" s="0">
         <x:v>27</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>98</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
         <x:v>1</x:v>
@@ -2241,157 +2298,163 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N30" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q30" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V30" s="0" t="s">
-        <x:v>99</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="X30" s="0" t="s">
-        <x:v>78</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:28">
+        <x:v>80</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:29">
       <x:c r="A31" s="0">
         <x:v>28</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>100</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D31" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G31" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O31" s="0" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="P31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="Q31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="R31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="S31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="T31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="U31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="V31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="W31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="X31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AA31" s="0" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="P31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="Q31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="R31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="S31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="T31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="U31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="V31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="W31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="X31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-      <x:c r="AA31" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="AB31" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC31" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:29">
       <x:c r="A32" s="0">
         <x:v>29</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D32" s="0">
-        <x:v>14</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="G32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P32" s="0" t="s">
-        <x:v>38</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="R32" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="S32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U32" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="V32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W32" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z32" s="0" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="AA32" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC32" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:29">
       <x:c r="A33" s="0">
         <x:v>30</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
         <x:v>1</x:v>
@@ -2400,142 +2463,148 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H33" s="0" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="J33" s="0" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="N33" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O33" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S33" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:28">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:29">
       <x:c r="A34" s="0">
         <x:v>31</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D34" s="0">
-        <x:v>18</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I34" s="0" t="s">
-        <x:v>36</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="J34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L34" s="0" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="M34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X34" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z34" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AA34" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC34" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:29">
       <x:c r="A35" s="0">
         <x:v>32</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D35" s="0">
-        <x:v>10</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="G35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L35" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N35" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="P35" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="W35" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="Z35" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:28">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="AC35" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:29">
       <x:c r="A36" s="0">
         <x:v>33</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
         <x:v>2</x:v>
@@ -2544,141 +2613,150 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="G36" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H36" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA36" s="0" t="s">
-        <x:v>111</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:28">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:29">
       <x:c r="A37" s="0">
         <x:v>34</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D37" s="0">
-        <x:v>20</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="G37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K37" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N37" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA37" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB37" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC37" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:29">
       <x:c r="A38" s="0">
         <x:v>35</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D38" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="G38" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S38" s="0" t="s">
-        <x:v>114</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:28">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="AC38" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:29">
       <x:c r="A39" s="0">
         <x:v>36</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>115</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D39" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="G39" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H39" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K39" s="0" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="W39" s="0" t="s">
-        <x:v>116</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:28">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="AC39" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:29">
       <x:c r="A40" s="0">
         <x:v>37</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>117</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
         <x:v>2</x:v>
@@ -2687,244 +2765,259 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="G40" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I40" s="0" t="s">
-        <x:v>118</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:28">
+        <x:v>124</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:29">
       <x:c r="A41" s="0">
         <x:v>38</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>119</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
         <x:v>2</x:v>
       </x:c>
       <x:c r="D41" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="G41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="H41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N41" s="0" t="s">
-        <x:v>27</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="O41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S41" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="T41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W41" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X41" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC41" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:29">
       <x:c r="A42" s="0">
         <x:v>39</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>120</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D42" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="H42" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I42" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J42" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K42" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O42" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="S42" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:28">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="AC42" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:29">
       <x:c r="A43" s="0">
         <x:v>40</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>122</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D43" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="H43" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I43" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R43" s="0" t="s">
-        <x:v>123</x:v>
+        <x:v>129</x:v>
       </x:c>
       <x:c r="AA43" s="0" t="s">
-        <x:v>124</x:v>
+        <x:v>130</x:v>
       </x:c>
       <x:c r="AB43" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC43" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:29">
       <x:c r="A44" s="0">
         <x:v>41</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>125</x:v>
+        <x:v>131</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
         <x:v>3</x:v>
       </x:c>
       <x:c r="D44" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="H44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="I44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K44" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N44" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q44" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S44" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="V44" s="0" t="s">
-        <x:v>86</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="X44" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Z44" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AA44" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC44" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:29">
       <x:c r="A45" s="0">
         <x:v>42</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>127</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D45" s="0">
-        <x:v>16</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="I45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="J45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R45" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="S45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y45" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z45" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC45" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:29">
       <x:c r="A46" s="0">
         <x:v>43</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>128</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
         <x:v>4</x:v>
@@ -2933,77 +3026,80 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="I46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K46" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="L46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O46" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S46" s="0" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="W46" s="0" t="s">
-        <x:v>32</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="X46" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:29">
       <x:c r="A47" s="0">
         <x:v>44</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>129</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
         <x:v>4</x:v>
       </x:c>
       <x:c r="D47" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="I47" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K47" s="0" t="s">
-        <x:v>37</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="S47" s="0" t="s">
-        <x:v>65</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="T47" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y47" s="0" t="s">
-        <x:v>130</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="Z47" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA47" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB47" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC47" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:29">
       <x:c r="A48" s="0">
         <x:v>45</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>131</x:v>
+        <x:v>137</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
         <x:v>4</x:v>
@@ -3012,39 +3108,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="I48" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M48" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="O48" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="Q48" s="0" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="S48" s="0" t="s">
         <x:v>132</x:v>
       </x:c>
-      <x:c r="O48" s="0" t="s">
-        <x:v>133</x:v>
-      </x:c>
-      <x:c r="Q48" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="S48" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
       <x:c r="T48" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X48" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="Y48" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA48" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:28">
+        <x:v>140</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:29">
       <x:c r="A49" s="0">
         <x:v>46</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>135</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
         <x:v>5</x:v>
@@ -3053,139 +3149,145 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="J49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M49" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R49" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="S49" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U49" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="X49" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:28">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:29">
       <x:c r="A50" s="0">
         <x:v>47</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>137</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D50" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="J50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N50" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="O50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R50" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="S50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W50" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="X50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z50" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AA50" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB50" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC50" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:29">
       <x:c r="A51" s="0">
         <x:v>48</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>140</x:v>
+        <x:v>146</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
         <x:v>5</x:v>
       </x:c>
       <x:c r="D51" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="J51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="K51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M51" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P51" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="S51" s="0" t="s">
-        <x:v>141</x:v>
+        <x:v>147</x:v>
       </x:c>
       <x:c r="T51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W51" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="X51" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z51" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AB51" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:28">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AC51" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:29">
       <x:c r="A52" s="0">
         <x:v>49</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>142</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
         <x:v>6</x:v>
@@ -3194,24 +3296,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="K52" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N52" s="0" t="s">
-        <x:v>138</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="T52" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="W52" s="0" t="s">
-        <x:v>139</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:28">
+        <x:v>145</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:29">
       <x:c r="A53" s="0">
         <x:v>50</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>144</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
         <x:v>6</x:v>
@@ -3220,33 +3322,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="K53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O53" s="0" t="s">
-        <x:v>121</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="P53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T53" s="0" t="s">
-        <x:v>145</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="U53" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X53" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:28">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:29">
       <x:c r="A54" s="0">
         <x:v>51</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>146</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
         <x:v>6</x:v>
@@ -3255,83 +3357,86 @@
         <x:v>11</x:v>
       </x:c>
       <x:c r="K54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N54" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q54" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S54" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="T54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X54" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="Z54" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AA54" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB54" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:29">
       <x:c r="A55" s="0">
         <x:v>52</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>147</x:v>
+        <x:v>153</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D55" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M55" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R55" s="0" t="s">
-        <x:v>85</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="S55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T55" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W55" s="0" t="s">
-        <x:v>139</x:v>
+        <x:v>145</x:v>
       </x:c>
       <x:c r="AA55" s="0" t="s">
-        <x:v>148</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:28">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="AC55" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:29">
       <x:c r="A56" s="0">
         <x:v>53</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>149</x:v>
+        <x:v>155</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
         <x:v>6</x:v>
@@ -3340,68 +3445,71 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="K56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N56" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O56" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q56" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S56" s="0" t="s">
-        <x:v>126</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:28">
+        <x:v>132</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:29">
       <x:c r="A57" s="0">
         <x:v>54</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>150</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D57" s="0">
-        <x:v>8</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="K57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N57" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="T57" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="U57" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W57" s="0" t="s">
-        <x:v>97</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="Y57" s="0" t="s">
-        <x:v>151</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="AB57" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:28">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="AC57" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:29">
       <x:c r="A58" s="0">
         <x:v>55</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>152</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
         <x:v>6</x:v>
@@ -3410,74 +3518,77 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L58" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N58" s="0" t="s">
-        <x:v>54</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="59" spans="1:28">
+        <x:v>56</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:29">
       <x:c r="A59" s="0">
         <x:v>56</x:v>
       </x:c>
       <x:c r="B59" s="0" t="s">
-        <x:v>153</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="C59" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D59" s="0">
-        <x:v>13</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="K59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R59" s="0" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="W59" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="X59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA59" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB59" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="60" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC59" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:29">
       <x:c r="A60" s="0">
         <x:v>57</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>155</x:v>
+        <x:v>161</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
         <x:v>6</x:v>
@@ -3486,21 +3597,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="K60" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W60" s="0" t="s">
-        <x:v>116</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="X60" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="61" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:29">
       <x:c r="A61" s="0">
         <x:v>58</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>156</x:v>
+        <x:v>162</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
         <x:v>6</x:v>
@@ -3509,92 +3620,95 @@
         <x:v>10</x:v>
       </x:c>
       <x:c r="K61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M61" s="0" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="N61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q61" s="0" t="s">
-        <x:v>157</x:v>
+        <x:v>163</x:v>
       </x:c>
       <x:c r="R61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W61" s="0" t="s">
-        <x:v>154</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="X61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z61" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB61" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="62" spans="1:28">
+        <x:v>63</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:29">
       <x:c r="A62" s="0">
         <x:v>59</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>158</x:v>
+        <x:v>164</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
       <x:c r="D62" s="0">
-        <x:v>12</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="K62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="L62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U62" s="0" t="s">
-        <x:v>159</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="Y62" s="0" t="s">
-        <x:v>160</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="Z62" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA62" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="63" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC62" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:29">
       <x:c r="A63" s="0">
         <x:v>60</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>161</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
         <x:v>7</x:v>
@@ -3603,27 +3717,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="L63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N63" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P63" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q63" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="64" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:29">
       <x:c r="A64" s="0">
         <x:v>61</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>162</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
         <x:v>7</x:v>
@@ -3632,36 +3746,36 @@
         <x:v>8</x:v>
       </x:c>
       <x:c r="L64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="N64" s="0" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="O64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="R64" s="0" t="s">
-        <x:v>70</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="S64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T64" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V64" s="0" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="AA64" s="0" t="s">
-        <x:v>136</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="65" spans="1:28">
+        <x:v>142</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:29">
       <x:c r="A65" s="0">
         <x:v>62</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>163</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
         <x:v>7</x:v>
@@ -3670,15 +3784,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="L65" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="66" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:29">
       <x:c r="A66" s="0">
         <x:v>63</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>164</x:v>
+        <x:v>170</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
         <x:v>7</x:v>
@@ -3687,33 +3801,33 @@
         <x:v>7</x:v>
       </x:c>
       <x:c r="L66" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="M66" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P66" s="0" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="U66" s="0" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="V66" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y66" s="0" t="s">
-        <x:v>165</x:v>
+        <x:v>171</x:v>
       </x:c>
       <x:c r="Z66" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="67" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:29">
       <x:c r="A67" s="0">
         <x:v>64</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>166</x:v>
+        <x:v>172</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
         <x:v>8</x:v>
@@ -3722,18 +3836,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="M67" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S67" s="0" t="s">
-        <x:v>167</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="68" spans="1:28">
+        <x:v>173</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:29">
       <x:c r="A68" s="0">
         <x:v>65</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>168</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
         <x:v>8</x:v>
@@ -3742,15 +3856,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M68" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="69" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:29">
       <x:c r="A69" s="0">
         <x:v>66</x:v>
       </x:c>
       <x:c r="B69" s="0" t="s">
-        <x:v>169</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="C69" s="0" t="s">
         <x:v>8</x:v>
@@ -3759,27 +3873,27 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="M69" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q69" s="0" t="s">
-        <x:v>170</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="S69" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="T69" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA69" s="0" t="s">
-        <x:v>171</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="70" spans="1:28">
+        <x:v>177</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:29">
       <x:c r="A70" s="0">
         <x:v>67</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>172</x:v>
+        <x:v>178</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
         <x:v>8</x:v>
@@ -3788,39 +3902,39 @@
         <x:v>9</x:v>
       </x:c>
       <x:c r="M70" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O70" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="Q70" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="S70" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="T70" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X70" s="0" t="s">
-        <x:v>71</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="Z70" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AA70" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB70" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="71" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:29">
       <x:c r="A71" s="0">
         <x:v>68</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>173</x:v>
+        <x:v>179</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
         <x:v>8</x:v>
@@ -3829,15 +3943,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="M71" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="72" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:29">
       <x:c r="A72" s="0">
         <x:v>69</x:v>
       </x:c>
       <x:c r="B72" s="0" t="s">
-        <x:v>174</x:v>
+        <x:v>180</x:v>
       </x:c>
       <x:c r="C72" s="0" t="s">
         <x:v>8</x:v>
@@ -3846,21 +3960,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="M72" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O72" s="0" t="s">
-        <x:v>133</x:v>
+        <x:v>139</x:v>
       </x:c>
       <x:c r="S72" s="0" t="s">
-        <x:v>106</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="73" spans="1:28">
+        <x:v>109</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:29">
       <x:c r="A73" s="0">
         <x:v>70</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>175</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
         <x:v>9</x:v>
@@ -3869,21 +3983,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O73" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P73" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="74" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:29">
       <x:c r="A74" s="0">
         <x:v>71</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>176</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
         <x:v>9</x:v>
@@ -3892,18 +4006,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="N74" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q74" s="0" t="s">
-        <x:v>157</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="75" spans="1:28">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:29">
       <x:c r="A75" s="0">
         <x:v>72</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>177</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
         <x:v>9</x:v>
@@ -3912,24 +4026,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="N75" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P75" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="Z75" s="0" t="s">
-        <x:v>178</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="AA75" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="76" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:29">
       <x:c r="A76" s="0">
         <x:v>73</x:v>
       </x:c>
       <x:c r="B76" s="0" t="s">
-        <x:v>179</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="C76" s="0" t="s">
         <x:v>9</x:v>
@@ -3938,30 +4052,30 @@
         <x:v>6</x:v>
       </x:c>
       <x:c r="N76" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="O76" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V76" s="0" t="s">
-        <x:v>180</x:v>
+        <x:v>186</x:v>
       </x:c>
       <x:c r="W76" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X76" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA76" s="0" t="s">
-        <x:v>67</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="77" spans="1:28">
+        <x:v>69</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:29">
       <x:c r="A77" s="0">
         <x:v>74</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>181</x:v>
+        <x:v>187</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
         <x:v>9</x:v>
@@ -3970,21 +4084,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="N77" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T77" s="0" t="s">
-        <x:v>143</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="U77" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="78" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:29">
       <x:c r="A78" s="0">
         <x:v>75</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>182</x:v>
+        <x:v>188</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
         <x:v>10</x:v>
@@ -3993,18 +4107,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O78" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q78" s="0" t="s">
-        <x:v>77</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="79" spans="1:28">
+        <x:v>79</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:29">
       <x:c r="A79" s="0">
         <x:v>76</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>183</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
         <x:v>10</x:v>
@@ -4013,21 +4127,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="O79" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q79" s="0" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="W79" s="0" t="s">
-        <x:v>184</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="80" spans="1:28">
+        <x:v>190</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:29">
       <x:c r="A80" s="0">
         <x:v>77</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>185</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
         <x:v>10</x:v>
@@ -4036,18 +4150,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="O80" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="P80" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="81" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:29">
       <x:c r="A81" s="0">
         <x:v>78</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>186</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
         <x:v>11</x:v>
@@ -4056,24 +4170,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P81" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W81" s="0" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="AA81" s="0" t="s">
-        <x:v>148</x:v>
+        <x:v>154</x:v>
       </x:c>
       <x:c r="AB81" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="82" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:29">
       <x:c r="A82" s="0">
         <x:v>79</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>187</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
         <x:v>11</x:v>
@@ -4082,24 +4196,24 @@
         <x:v>4</x:v>
       </x:c>
       <x:c r="P82" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Q82" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S82" s="0" t="s">
-        <x:v>126</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="V82" s="0" t="s">
-        <x:v>86</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="83" spans="1:28">
+        <x:v>88</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:29">
       <x:c r="A83" s="0">
         <x:v>80</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>188</x:v>
+        <x:v>194</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
         <x:v>12</x:v>
@@ -4108,21 +4222,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Q83" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W83" s="0" t="s">
-        <x:v>184</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="Z83" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="84" spans="1:28">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:29">
       <x:c r="A84" s="0">
         <x:v>81</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>189</x:v>
+        <x:v>195</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
         <x:v>13</x:v>
@@ -4131,50 +4245,53 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="R84" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="85" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:29">
       <x:c r="A85" s="0">
         <x:v>82</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>190</x:v>
+        <x:v>196</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D85" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="R85" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S85" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U85" s="0" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="X85" s="0" t="s">
-        <x:v>136</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="Y85" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA85" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="AB85" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="86" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC85" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:29">
       <x:c r="A86" s="0">
         <x:v>83</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>191</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
         <x:v>13</x:v>
@@ -4183,21 +4300,21 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="R86" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S86" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T86" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="87" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:29">
       <x:c r="A87" s="0">
         <x:v>84</x:v>
       </x:c>
       <x:c r="B87" s="0" t="s">
-        <x:v>192</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C87" s="0" t="s">
         <x:v>13</x:v>
@@ -4206,47 +4323,50 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="R87" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S87" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="T87" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="U87" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V87" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="88" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:29">
       <x:c r="A88" s="0">
         <x:v>85</x:v>
       </x:c>
       <x:c r="B88" s="0" t="s">
-        <x:v>193</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="C88" s="0" t="s">
         <x:v>13</x:v>
       </x:c>
       <x:c r="D88" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="R88" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="V88" s="0" t="s">
-        <x:v>194</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="89" spans="1:28">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="AC88" s="0" t="s">
+        <x:v>201</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:29">
       <x:c r="A89" s="0">
         <x:v>86</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>195</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
         <x:v>13</x:v>
@@ -4255,18 +4375,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="R89" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="S89" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="90" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:29">
       <x:c r="A90" s="0">
         <x:v>87</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>196</x:v>
+        <x:v>203</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
         <x:v>14</x:v>
@@ -4275,18 +4395,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S90" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z90" s="0" t="s">
-        <x:v>197</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="91" spans="1:28">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:29">
       <x:c r="A91" s="0">
         <x:v>88</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>198</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
         <x:v>14</x:v>
@@ -4295,114 +4415,123 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="S91" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W91" s="0" t="s">
-        <x:v>32</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="92" spans="1:28">
+        <x:v>33</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:29">
       <x:c r="A92" s="0">
         <x:v>89</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>199</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D92" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="V92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y92" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA92" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="AB92" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="93" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC92" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:29">
       <x:c r="A93" s="0">
         <x:v>90</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>200</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D93" s="0">
-        <x:v>7</x:v>
+        <x:v>8</x:v>
       </x:c>
       <x:c r="V93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA93" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB93" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="94" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC93" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:29">
       <x:c r="A94" s="0">
         <x:v>91</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>201</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
         <x:v>17</x:v>
       </x:c>
       <x:c r="D94" s="0">
-        <x:v>5</x:v>
+        <x:v>6</x:v>
       </x:c>
       <x:c r="V94" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="W94" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X94" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z94" s="0" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="AA94" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="95" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC94" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:29">
       <x:c r="A95" s="0">
         <x:v>92</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>202</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
         <x:v>17</x:v>
@@ -4411,15 +4540,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="V95" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="96" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:29">
       <x:c r="A96" s="0">
         <x:v>93</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>203</x:v>
+        <x:v>210</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
         <x:v>17</x:v>
@@ -4428,59 +4557,62 @@
         <x:v>5</x:v>
       </x:c>
       <x:c r="V96" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X96" s="0" t="s">
-        <x:v>78</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="Y96" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z96" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA96" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="97" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:29">
       <x:c r="A97" s="0">
         <x:v>94</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>204</x:v>
+        <x:v>211</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D97" s="0">
-        <x:v>6</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="W97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA97" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB97" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="98" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC97" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:29">
       <x:c r="A98" s="0">
         <x:v>95</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>205</x:v>
+        <x:v>212</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
         <x:v>18</x:v>
@@ -4489,15 +4621,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="W98" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="99" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:29">
       <x:c r="A99" s="0">
         <x:v>96</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>206</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
         <x:v>18</x:v>
@@ -4506,18 +4638,18 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="W99" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z99" s="0" t="s">
-        <x:v>87</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="100" spans="1:28">
+        <x:v>89</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:29">
       <x:c r="A100" s="0">
         <x:v>97</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>207</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
         <x:v>18</x:v>
@@ -4526,44 +4658,47 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="W100" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB100" s="0" t="s">
-        <x:v>208</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="101" spans="1:28">
+        <x:v>215</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" spans="1:29">
       <x:c r="A101" s="0">
         <x:v>98</x:v>
       </x:c>
       <x:c r="B101" s="0" t="s">
-        <x:v>209</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="C101" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D101" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W101" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X101" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y101" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA101" s="0" t="s">
-        <x:v>134</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="102" spans="1:28">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="AC101" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="102" spans="1:29">
       <x:c r="A102" s="0">
         <x:v>99</x:v>
       </x:c>
       <x:c r="B102" s="0" t="s">
-        <x:v>210</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="C102" s="0" t="s">
         <x:v>18</x:v>
@@ -4572,44 +4707,47 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="W102" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X102" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="103" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="103" spans="1:29">
       <x:c r="A103" s="0">
         <x:v>100</x:v>
       </x:c>
       <x:c r="B103" s="0" t="s">
-        <x:v>211</x:v>
+        <x:v>218</x:v>
       </x:c>
       <x:c r="C103" s="0" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="D103" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="W103" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="X103" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA103" s="0" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="AB103" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="104" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC103" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="104" spans="1:29">
       <x:c r="A104" s="0">
         <x:v>101</x:v>
       </x:c>
       <x:c r="B104" s="0" t="s">
-        <x:v>212</x:v>
+        <x:v>219</x:v>
       </x:c>
       <x:c r="C104" s="0" t="s">
         <x:v>19</x:v>
@@ -4618,35 +4756,38 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="X104" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="105" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="105" spans="1:29">
       <x:c r="A105" s="0">
         <x:v>102</x:v>
       </x:c>
       <x:c r="B105" s="0" t="s">
-        <x:v>213</x:v>
+        <x:v>220</x:v>
       </x:c>
       <x:c r="C105" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D105" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="X105" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y105" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="106" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC105" s="0" t="s">
+        <x:v>221</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="106" spans="1:29">
       <x:c r="A106" s="0">
         <x:v>103</x:v>
       </x:c>
       <x:c r="B106" s="0" t="s">
-        <x:v>214</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C106" s="0" t="s">
         <x:v>19</x:v>
@@ -4655,15 +4796,15 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="X106" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="107" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="107" spans="1:29">
       <x:c r="A107" s="0">
         <x:v>104</x:v>
       </x:c>
       <x:c r="B107" s="0" t="s">
-        <x:v>215</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="C107" s="0" t="s">
         <x:v>19</x:v>
@@ -4672,41 +4813,44 @@
         <x:v>1</x:v>
       </x:c>
       <x:c r="X107" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="108" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="108" spans="1:29">
       <x:c r="A108" s="0">
         <x:v>105</x:v>
       </x:c>
       <x:c r="B108" s="0" t="s">
-        <x:v>216</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="C108" s="0" t="s">
         <x:v>19</x:v>
       </x:c>
       <x:c r="D108" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="X108" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y108" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z108" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB108" s="0" t="s">
-        <x:v>61</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="109" spans="1:28">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="AC108" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="109" spans="1:29">
       <x:c r="A109" s="0">
         <x:v>106</x:v>
       </x:c>
       <x:c r="B109" s="0" t="s">
-        <x:v>217</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="C109" s="0" t="s">
         <x:v>19</x:v>
@@ -4715,47 +4859,50 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="X109" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Y109" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB109" s="0" t="s">
-        <x:v>34</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="110" spans="1:28">
+        <x:v>35</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="110" spans="1:29">
       <x:c r="A110" s="0">
         <x:v>107</x:v>
       </x:c>
       <x:c r="B110" s="0" t="s">
-        <x:v>218</x:v>
+        <x:v>226</x:v>
       </x:c>
       <x:c r="C110" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D110" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y110" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z110" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA110" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB110" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="111" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC110" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="111" spans="1:29">
       <x:c r="A111" s="0">
         <x:v>108</x:v>
       </x:c>
       <x:c r="B111" s="0" t="s">
-        <x:v>219</x:v>
+        <x:v>227</x:v>
       </x:c>
       <x:c r="C111" s="0" t="s">
         <x:v>20</x:v>
@@ -4764,73 +4911,79 @@
         <x:v>3</x:v>
       </x:c>
       <x:c r="Y111" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA111" s="0" t="s">
-        <x:v>134</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="AB111" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="112" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="112" spans="1:29">
       <x:c r="A112" s="0">
         <x:v>109</x:v>
       </x:c>
       <x:c r="B112" s="0" t="s">
-        <x:v>220</x:v>
+        <x:v>228</x:v>
       </x:c>
       <x:c r="C112" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D112" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y112" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z112" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA112" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB112" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="113" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC112" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="113" spans="1:29">
       <x:c r="A113" s="0">
         <x:v>110</x:v>
       </x:c>
       <x:c r="B113" s="0" t="s">
-        <x:v>221</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="C113" s="0" t="s">
         <x:v>20</x:v>
       </x:c>
       <x:c r="D113" s="0">
-        <x:v>4</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="Y113" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="Z113" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AA113" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB113" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="114" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC113" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="114" spans="1:29">
       <x:c r="A114" s="0">
         <x:v>111</x:v>
       </x:c>
       <x:c r="B114" s="0" t="s">
-        <x:v>222</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C114" s="0" t="s">
         <x:v>22</x:v>
@@ -4839,98 +4992,147 @@
         <x:v>2</x:v>
       </x:c>
       <x:c r="AA114" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB114" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="115" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="115" spans="1:29">
       <x:c r="A115" s="0">
         <x:v>112</x:v>
       </x:c>
       <x:c r="B115" s="0" t="s">
-        <x:v>223</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="C115" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D115" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AA115" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="116" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC115" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="116" spans="1:29">
       <x:c r="A116" s="0">
         <x:v>113</x:v>
       </x:c>
       <x:c r="B116" s="0" t="s">
-        <x:v>224</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="C116" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D116" s="0">
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="AA116" s="0" t="s">
-        <x:v>25</x:v>
+        <x:v>26</x:v>
       </x:c>
       <x:c r="AB116" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="117" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC116" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="117" spans="1:29">
       <x:c r="A117" s="0">
         <x:v>114</x:v>
       </x:c>
       <x:c r="B117" s="0" t="s">
-        <x:v>225</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="C117" s="0" t="s">
         <x:v>22</x:v>
       </x:c>
       <x:c r="D117" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AA117" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="118" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC117" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="118" spans="1:29">
       <x:c r="A118" s="0">
         <x:v>115</x:v>
       </x:c>
       <x:c r="B118" s="0" t="s">
-        <x:v>226</x:v>
+        <x:v>234</x:v>
       </x:c>
       <x:c r="C118" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D118" s="0">
-        <x:v>1</x:v>
+        <x:v>2</x:v>
       </x:c>
       <x:c r="AB118" s="0" t="s">
-        <x:v>25</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="119" spans="1:28">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC118" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="119" spans="1:29">
       <x:c r="A119" s="0">
         <x:v>116</x:v>
       </x:c>
       <x:c r="B119" s="0" t="s">
-        <x:v>227</x:v>
+        <x:v>235</x:v>
       </x:c>
       <x:c r="C119" s="0" t="s">
         <x:v>23</x:v>
       </x:c>
       <x:c r="D119" s="0">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="AB119" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+      <x:c r="AC119" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="120" spans="1:29">
+      <x:c r="A120" s="0">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="B120" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+      <x:c r="C120" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D120" s="0">
         <x:v>1</x:v>
       </x:c>
-      <x:c r="AB119" s="0" t="s">
-        <x:v>25</x:v>
+      <x:c r="AC120" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="121" spans="1:29">
+      <x:c r="A121" s="0">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="B121" s="0" t="s">
+        <x:v>237</x:v>
+      </x:c>
+      <x:c r="C121" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="D121" s="0">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="AC121" s="0" t="s">
+        <x:v>26</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
